--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
@@ -66,10 +66,10 @@
   </sheetData>
   <autoFilter ref="A1:B1"/>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="A2:A1001">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A1001">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B1001">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="B2:B1001">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInferenceCanBeDisabled.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -74,4 +74,13 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Employees">
+    <column index="1" property="Age"/>
+    <column index="2" property="IsActive"/>
+  </sheet>
+</columnMetadata>
 </file>